--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A46C0E-EE86-4721-ABBE-F7F6518608B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886DE556-7543-4F81-9DC8-70FB795B28B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20790" yWindow="5115" windowWidth="28725" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10170" yWindow="3495" windowWidth="28725" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +201,14 @@
   </si>
   <si>
     <t>112,0,109</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>16,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>16,0,50</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -261,13 +269,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.499984740745262"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -301,7 +309,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -320,20 +328,23 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -605,13 +616,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
-    <col min="4" max="5" width="10" style="7" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -631,10 +642,10 @@
       <c r="E1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -660,10 +671,10 @@
       <c r="E2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -689,10 +700,10 @@
       <c r="E3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -712,12 +723,14 @@
       <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="9" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -737,12 +750,14 @@
       <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="9" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9">
+        <v>2</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -762,12 +777,14 @@
       <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9">
         <v>3</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="10" t="s">
+      <c r="F6" s="11">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -787,12 +804,14 @@
       <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9">
         <v>4</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="9" t="s">
+      <c r="F7" s="11">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -812,12 +831,14 @@
       <c r="C8" s="3">
         <v>1</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9">
         <v>5</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="9" t="s">
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="3" t="s">
@@ -837,12 +858,14 @@
       <c r="C9" s="3">
         <v>1</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9">
         <v>6</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>43</v>
       </c>
       <c r="H9" s="3" t="s">
@@ -862,14 +885,14 @@
       <c r="C10" s="3">
         <v>2</v>
       </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6">
-        <v>6</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -889,14 +912,14 @@
       <c r="C11" s="3">
         <v>2</v>
       </c>
-      <c r="D11" s="6">
-        <v>2</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6">
-        <v>6</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -916,14 +939,14 @@
       <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="9">
         <v>3</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6">
-        <v>6</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="E12" s="9"/>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
@@ -943,12 +966,14 @@
       <c r="C13" s="4">
         <v>1</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="10" t="s">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>31</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -968,12 +993,14 @@
       <c r="C14" s="4">
         <v>1</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="10" t="s">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9">
+        <v>2</v>
+      </c>
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -993,12 +1020,14 @@
       <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9">
         <v>3</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>32</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -1018,12 +1047,14 @@
       <c r="C16" s="4">
         <v>1</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9">
         <v>4</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="11">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -1043,12 +1074,14 @@
       <c r="C17" s="4">
         <v>1</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9">
         <v>5</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="10" t="s">
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -1068,12 +1101,14 @@
       <c r="C18" s="4">
         <v>1</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6">
+      <c r="D18" s="9"/>
+      <c r="E18" s="9">
         <v>6</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="10" t="s">
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>44</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -1093,12 +1128,14 @@
       <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6">
+      <c r="D19" s="9"/>
+      <c r="E19" s="9">
         <v>7</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="10" t="s">
+      <c r="F19" s="11">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -1118,12 +1155,14 @@
       <c r="C20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9">
         <v>7</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="10" t="s">
+      <c r="F20" s="11">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>49</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -1143,14 +1182,14 @@
       <c r="C21" s="4">
         <v>2</v>
       </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6">
-        <v>6</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="D21" s="9">
+        <v>1</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="11">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -1170,14 +1209,14 @@
       <c r="C22" s="4">
         <v>2</v>
       </c>
-      <c r="D22" s="6">
-        <v>2</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6">
-        <v>6</v>
-      </c>
-      <c r="G22" s="10" t="s">
+      <c r="D22" s="9">
+        <v>2</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="11">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>36</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -1197,20 +1236,74 @@
       <c r="C23" s="4">
         <v>2</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="9">
         <v>3</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6">
-        <v>6</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="E23" s="9"/>
+      <c r="F23" s="11">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>37</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+      <c r="D24" s="9">
+        <v>3</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="11">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="9">
+        <v>3</v>
+      </c>
+      <c r="E25" s="9"/>
+      <c r="F25" s="11">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="4">
         <v>1</v>
       </c>
     </row>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886DE556-7543-4F81-9DC8-70FB795B28B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7F4C83-37E2-446F-8D01-EB6CD0EA757A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10170" yWindow="3495" windowWidth="28725" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12390" yWindow="4200" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -208,7 +208,51 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>16,0,50</t>
+    <t>30,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>31,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>16,0,42</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大兵1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大兵2</t>
+  </si>
+  <si>
+    <t>大兵3</t>
+  </si>
+  <si>
+    <t>大兵4</t>
+  </si>
+  <si>
+    <t>大兵5</t>
+  </si>
+  <si>
+    <t>32,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>33,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>34,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>35,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>36,0,40</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -616,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
@@ -1298,12 +1342,201 @@
         <v>0</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>23</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4">
+        <v>2</v>
+      </c>
+      <c r="D26" s="9">
+        <v>1</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="11">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4">
+        <v>2</v>
+      </c>
+      <c r="D27" s="9">
+        <v>1</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="11">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>25</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4">
+        <v>2</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="11">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="9">
+        <v>1</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="11">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>27</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30" s="9">
+        <v>1</v>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="11">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9"/>
+      <c r="F31" s="11">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>29</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32" s="9">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="11">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" s="4">
         <v>1</v>
       </c>
     </row>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7F4C83-37E2-446F-8D01-EB6CD0EA757A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821352EB-E919-4734-A548-B92F21E0A26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12390" yWindow="4200" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17940" yWindow="3315" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -107,22 +107,6 @@
     <t>坦克</t>
   </si>
   <si>
-    <t>16,0,16</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>16,0,12</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>12,0,16</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,0,10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>5,0,5</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -253,6 +237,22 @@
   </si>
   <si>
     <t>36,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,0,15</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,18</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,0,20</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -684,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>4</v>
@@ -696,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -713,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>8</v>
@@ -725,7 +725,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -774,8 +774,8 @@
       <c r="F4" s="11">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>27</v>
+      <c r="G4" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>17</v>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>18</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>19</v>
@@ -936,8 +936,8 @@
       <c r="F10" s="11">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>24</v>
+      <c r="G10" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>20</v>
@@ -963,8 +963,8 @@
       <c r="F11" s="11">
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>25</v>
+      <c r="G11" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>21</v>
@@ -990,8 +990,8 @@
       <c r="F12" s="11">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>26</v>
+      <c r="G12" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>15</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>17</v>
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>18</v>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>19</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -1207,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>23</v>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>23</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>23</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>23</v>
@@ -1342,7 +1342,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>23</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -1396,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I27" s="4">
         <v>1</v>
@@ -1423,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I28" s="4">
         <v>1</v>
@@ -1450,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
@@ -1477,10 +1477,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
@@ -1504,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I32" s="4">
         <v>1</v>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821352EB-E919-4734-A548-B92F21E0A26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B390D2-5AA5-4B50-990A-0D53BD6AF382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17940" yWindow="3315" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1395" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -111,14 +111,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>5,0,10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,0,5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>117,0,117</t>
   </si>
   <si>
@@ -188,10 +180,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>16,0,40</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>30,0,40</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -200,10 +188,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>16,0,42</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>大兵1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -253,6 +237,22 @@
   </si>
   <si>
     <t>18,0,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,0,15</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,45</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,48</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -684,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>4</v>
@@ -696,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -713,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>8</v>
@@ -725,7 +725,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -855,8 +855,8 @@
       <c r="F7" s="11">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>25</v>
+      <c r="G7" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>18</v>
@@ -882,11 +882,11 @@
       <c r="F8" s="11">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>26</v>
+      <c r="G8" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>19</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>20</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>21</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>15</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>17</v>
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>18</v>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>19</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -1207,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>23</v>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>23</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>23</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>23</v>
@@ -1342,7 +1342,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>23</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -1396,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I27" s="4">
         <v>1</v>
@@ -1423,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I28" s="4">
         <v>1</v>
@@ -1450,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
@@ -1477,10 +1477,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
@@ -1504,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I32" s="4">
         <v>1</v>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B390D2-5AA5-4B50-990A-0D53BD6AF382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF1754B-B421-40C9-AB85-337B91043D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1395" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3615" yWindow="3090" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -95,9 +95,6 @@
     <t>坦克工厂</t>
   </si>
   <si>
-    <t>坦克1</t>
-  </si>
-  <si>
     <t>坦克2</t>
   </si>
   <si>
@@ -111,18 +108,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>117,0,117</t>
-  </si>
-  <si>
-    <t>122,0,122</t>
-  </si>
-  <si>
-    <t>122,0,117</t>
-  </si>
-  <si>
-    <t>117,0,122</t>
-  </si>
-  <si>
     <t>111,0,111</t>
   </si>
   <si>
@@ -156,10 +141,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>112,0,122</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Enabled</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -168,18 +149,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>防御塔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>109,0,112</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>112,0,109</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>30,0,40</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -253,6 +222,74 @@
   </si>
   <si>
     <t>20,0,48</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>115,0,115</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>120,0,120</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>120,0,110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>120,0,100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,120</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,120</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御塔1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御塔2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御塔3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御塔4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御塔5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,103</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>103,0,110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>95,0,115</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>115,0,95</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -298,7 +335,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,6 +357,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -353,7 +396,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -392,6 +435,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
@@ -684,7 +733,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>4</v>
@@ -696,7 +745,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -713,7 +762,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>8</v>
@@ -725,7 +774,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -742,10 +791,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -754,7 +803,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -775,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -802,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -819,130 +868,130 @@
         <v>1</v>
       </c>
       <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9"/>
       <c r="F6" s="11">
         <v>0</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="11">
         <v>0</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" s="11">
         <v>0</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F9" s="11">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2</v>
-      </c>
-      <c r="D10" s="9">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9"/>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9">
+        <v>4</v>
+      </c>
       <c r="F10" s="11">
         <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="3">
+        <v>59</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="4">
         <v>1</v>
       </c>
     </row>
@@ -950,26 +999,26 @@
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2</v>
-      </c>
-      <c r="E11" s="9"/>
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9">
+        <v>4</v>
+      </c>
       <c r="F11" s="11">
         <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="3">
+        <v>60</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="4">
         <v>1</v>
       </c>
     </row>
@@ -977,26 +1026,26 @@
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="9">
-        <v>3</v>
-      </c>
-      <c r="E12" s="9"/>
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9">
+        <v>5</v>
+      </c>
       <c r="F12" s="11">
         <v>0</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3">
+        <v>61</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="4">
         <v>1</v>
       </c>
     </row>
@@ -1012,16 +1061,16 @@
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F13" s="11">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
@@ -1039,16 +1088,16 @@
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F14" s="11">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -1066,16 +1115,16 @@
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F15" s="11">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -1093,16 +1142,16 @@
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16" s="11">
         <v>0</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -1120,16 +1169,16 @@
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -1147,397 +1196,505 @@
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9">
+        <v>7</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>101</v>
+      </c>
+      <c r="B19" s="13">
+        <v>1</v>
+      </c>
+      <c r="C19" s="13">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13">
+        <v>3</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>102</v>
+      </c>
+      <c r="B20" s="13">
+        <v>1</v>
+      </c>
+      <c r="C20" s="13">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13">
+        <v>4</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>103</v>
+      </c>
+      <c r="B21" s="13">
+        <v>1</v>
+      </c>
+      <c r="C21" s="13">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13">
+        <v>5</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>104</v>
+      </c>
+      <c r="B22" s="13">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13">
         <v>6</v>
       </c>
-      <c r="F18" s="11">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>105</v>
+      </c>
+      <c r="B23" s="13">
+        <v>1</v>
+      </c>
+      <c r="C23" s="13">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>106</v>
+      </c>
+      <c r="B24" s="13">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13">
+        <v>2</v>
+      </c>
+      <c r="D24" s="13">
+        <v>3</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>107</v>
+      </c>
+      <c r="B25" s="13">
+        <v>2</v>
+      </c>
+      <c r="C25" s="13">
+        <v>2</v>
+      </c>
+      <c r="D25" s="13">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>108</v>
+      </c>
+      <c r="B26" s="13">
+        <v>2</v>
+      </c>
+      <c r="C26" s="13">
+        <v>2</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2</v>
+      </c>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>109</v>
+      </c>
+      <c r="B27" s="13">
+        <v>2</v>
+      </c>
+      <c r="C27" s="13">
+        <v>2</v>
+      </c>
+      <c r="D27" s="13">
+        <v>3</v>
+      </c>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>110</v>
+      </c>
+      <c r="B28" s="13">
+        <v>2</v>
+      </c>
+      <c r="C28" s="13">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13">
+        <v>3</v>
+      </c>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>111</v>
+      </c>
+      <c r="B29" s="13">
+        <v>2</v>
+      </c>
+      <c r="C29" s="13">
+        <v>2</v>
+      </c>
+      <c r="D29" s="13">
+        <v>3</v>
+      </c>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>112</v>
+      </c>
+      <c r="B30" s="13">
+        <v>2</v>
+      </c>
+      <c r="C30" s="13">
+        <v>2</v>
+      </c>
+      <c r="D30" s="13">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I30" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>113</v>
+      </c>
+      <c r="B31" s="13">
+        <v>2</v>
+      </c>
+      <c r="C31" s="13">
+        <v>2</v>
+      </c>
+      <c r="D31" s="13">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4">
-        <v>2</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9">
-        <v>7</v>
-      </c>
-      <c r="F19" s="11">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7" t="s">
+      <c r="I31" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>114</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2</v>
+      </c>
+      <c r="C32" s="13">
+        <v>2</v>
+      </c>
+      <c r="D32" s="13">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H32" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>115</v>
+      </c>
+      <c r="B33" s="13">
+        <v>2</v>
+      </c>
+      <c r="C33" s="13">
+        <v>2</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>116</v>
+      </c>
+      <c r="B34" s="13">
+        <v>2</v>
+      </c>
+      <c r="C34" s="13">
+        <v>2</v>
+      </c>
+      <c r="D34" s="13">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>17</v>
-      </c>
-      <c r="B20" s="4">
-        <v>2</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9">
-        <v>7</v>
-      </c>
-      <c r="F20" s="11">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="I34" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>117</v>
+      </c>
+      <c r="B35" s="13">
+        <v>2</v>
+      </c>
+      <c r="C35" s="13">
+        <v>2</v>
+      </c>
+      <c r="D35" s="13">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I20" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4">
-        <v>2</v>
-      </c>
-      <c r="C21" s="4">
-        <v>2</v>
-      </c>
-      <c r="D21" s="9">
-        <v>1</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="11">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>19</v>
-      </c>
-      <c r="B22" s="4">
-        <v>2</v>
-      </c>
-      <c r="C22" s="4">
-        <v>2</v>
-      </c>
-      <c r="D22" s="9">
-        <v>2</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="11">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>20</v>
-      </c>
-      <c r="B23" s="4">
-        <v>2</v>
-      </c>
-      <c r="C23" s="4">
-        <v>2</v>
-      </c>
-      <c r="D23" s="9">
-        <v>3</v>
-      </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="11">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>21</v>
-      </c>
-      <c r="B24" s="4">
-        <v>2</v>
-      </c>
-      <c r="C24" s="4">
-        <v>2</v>
-      </c>
-      <c r="D24" s="9">
-        <v>3</v>
-      </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="11">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>22</v>
-      </c>
-      <c r="B25" s="4">
-        <v>2</v>
-      </c>
-      <c r="C25" s="4">
-        <v>2</v>
-      </c>
-      <c r="D25" s="9">
-        <v>3</v>
-      </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="11">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>23</v>
-      </c>
-      <c r="B26" s="4">
-        <v>2</v>
-      </c>
-      <c r="C26" s="4">
-        <v>2</v>
-      </c>
-      <c r="D26" s="9">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="11">
-        <v>0</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="4" t="s">
+      <c r="I35" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>118</v>
+      </c>
+      <c r="B36" s="13">
+        <v>2</v>
+      </c>
+      <c r="C36" s="13">
+        <v>2</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>24</v>
-      </c>
-      <c r="B27" s="4">
-        <v>2</v>
-      </c>
-      <c r="C27" s="4">
-        <v>2</v>
-      </c>
-      <c r="D27" s="9">
-        <v>1</v>
-      </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="11">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>25</v>
-      </c>
-      <c r="B28" s="4">
-        <v>2</v>
-      </c>
-      <c r="C28" s="4">
-        <v>2</v>
-      </c>
-      <c r="D28" s="9">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="11">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>26</v>
-      </c>
-      <c r="B29" s="4">
-        <v>2</v>
-      </c>
-      <c r="C29" s="4">
-        <v>2</v>
-      </c>
-      <c r="D29" s="9">
-        <v>1</v>
-      </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="11">
-        <v>0</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I29" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>27</v>
-      </c>
-      <c r="B30" s="4">
-        <v>2</v>
-      </c>
-      <c r="C30" s="4">
-        <v>2</v>
-      </c>
-      <c r="D30" s="9">
-        <v>1</v>
-      </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="11">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I30" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>28</v>
-      </c>
-      <c r="B31" s="4">
-        <v>2</v>
-      </c>
-      <c r="C31" s="4">
-        <v>2</v>
-      </c>
-      <c r="D31" s="9">
-        <v>1</v>
-      </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="11">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I31" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <v>29</v>
-      </c>
-      <c r="B32" s="4">
-        <v>2</v>
-      </c>
-      <c r="C32" s="4">
-        <v>2</v>
-      </c>
-      <c r="D32" s="9">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="11">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1</v>
+      <c r="H36" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" s="13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF1754B-B421-40C9-AB85-337B91043D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB6549-7048-440D-B634-45C3ACF609B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="3090" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16815" yWindow="2835" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -108,15 +108,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>111,0,111</t>
-  </si>
-  <si>
-    <t>111,0,115</t>
-  </si>
-  <si>
-    <t>115,0,111</t>
-  </si>
-  <si>
     <t>ConfID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -290,6 +281,18 @@
   </si>
   <si>
     <t>115,0,95</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,0,100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,100</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -733,7 +736,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>4</v>
@@ -745,7 +748,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -762,7 +765,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>8</v>
@@ -774,7 +777,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -791,10 +794,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -803,7 +806,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -824,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -878,13 +881,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -905,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>15</v>
@@ -932,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>16</v>
@@ -959,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>17</v>
@@ -986,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>18</v>
@@ -1013,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>18</v>
@@ -1040,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -1067,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>19</v>
@@ -1094,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -1121,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -1148,10 +1151,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -1175,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -1202,10 +1205,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -1256,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>18</v>
@@ -1283,10 +1286,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I21" s="13">
         <v>0</v>
@@ -1310,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>19</v>
@@ -1337,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>20</v>
@@ -1364,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>21</v>
@@ -1391,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>22</v>
@@ -1418,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>22</v>
@@ -1445,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>22</v>
@@ -1472,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>22</v>
@@ -1499,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>22</v>
@@ -1526,10 +1529,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I30" s="13">
         <v>0</v>
@@ -1553,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I31" s="13">
         <v>0</v>
@@ -1580,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I32" s="13">
         <v>0</v>
@@ -1607,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I33" s="13">
         <v>0</v>
@@ -1634,10 +1637,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I34" s="13">
         <v>0</v>
@@ -1661,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I35" s="13">
         <v>0</v>
@@ -1688,10 +1691,10 @@
         <v>0</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I36" s="13">
         <v>0</v>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB6549-7048-440D-B634-45C3ACF609B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724EC5E5-9C88-48A1-8C64-FEF2BBE968DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16815" yWindow="2835" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7050" yWindow="4215" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -264,26 +264,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>防御塔5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>110,0,103</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>103,0,110</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>95,0,115</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>115,0,95</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>100,0,105</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -293,6 +273,18 @@
   </si>
   <si>
     <t>100,0,100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,0,105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>115,0,105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,0,115</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -712,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
@@ -1097,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>60</v>
@@ -1124,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>61</v>
@@ -1151,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>62</v>
@@ -1178,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>63</v>
@@ -1188,35 +1180,35 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4">
-        <v>2</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9">
-        <v>7</v>
-      </c>
-      <c r="F18" s="11">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1</v>
+      <c r="A18" s="13">
+        <v>101</v>
+      </c>
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+      <c r="C18" s="13">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13">
+        <v>3</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B19" s="13">
         <v>1</v>
@@ -1226,16 +1218,16 @@
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="13">
         <v>0</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="13">
         <v>0</v>
@@ -1243,7 +1235,7 @@
     </row>
     <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" s="13">
         <v>1</v>
@@ -1253,16 +1245,16 @@
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="13">
         <v>0</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I20" s="13">
         <v>0</v>
@@ -1270,7 +1262,7 @@
     </row>
     <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B21" s="13">
         <v>1</v>
@@ -1280,16 +1272,16 @@
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="13">
         <v>0</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I21" s="13">
         <v>0</v>
@@ -1297,26 +1289,26 @@
     </row>
     <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B22" s="13">
         <v>1</v>
       </c>
       <c r="C22" s="13">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13">
-        <v>6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2</v>
+      </c>
+      <c r="E22" s="13"/>
       <c r="F22" s="13">
         <v>0</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="13">
         <v>0</v>
@@ -1324,7 +1316,7 @@
     </row>
     <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" s="13">
         <v>1</v>
@@ -1333,17 +1325,17 @@
         <v>2</v>
       </c>
       <c r="D23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13">
         <v>0</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I23" s="13">
         <v>0</v>
@@ -1351,26 +1343,26 @@
     </row>
     <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B24" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="13">
         <v>2</v>
       </c>
       <c r="D24" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13">
         <v>0</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" s="13">
         <v>0</v>
@@ -1378,7 +1370,7 @@
     </row>
     <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="13">
         <v>2</v>
@@ -1387,14 +1379,14 @@
         <v>2</v>
       </c>
       <c r="D25" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="13">
         <v>0</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>22</v>
@@ -1405,7 +1397,7 @@
     </row>
     <row r="26" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="13">
         <v>2</v>
@@ -1414,14 +1406,14 @@
         <v>2</v>
       </c>
       <c r="D26" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13">
         <v>0</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>22</v>
@@ -1432,7 +1424,7 @@
     </row>
     <row r="27" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="13">
         <v>2</v>
@@ -1448,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>22</v>
@@ -1459,7 +1451,7 @@
     </row>
     <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="13">
         <v>2</v>
@@ -1475,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>22</v>
@@ -1486,7 +1478,7 @@
     </row>
     <row r="29" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="13">
         <v>2</v>
@@ -1495,17 +1487,17 @@
         <v>2</v>
       </c>
       <c r="D29" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="13">
         <v>0</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I29" s="13">
         <v>0</v>
@@ -1513,7 +1505,7 @@
     </row>
     <row r="30" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" s="13">
         <v>2</v>
@@ -1529,10 +1521,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I30" s="13">
         <v>0</v>
@@ -1540,7 +1532,7 @@
     </row>
     <row r="31" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="13">
         <v>2</v>
@@ -1556,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I31" s="13">
         <v>0</v>
@@ -1567,7 +1559,7 @@
     </row>
     <row r="32" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" s="13">
         <v>2</v>
@@ -1583,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I32" s="13">
         <v>0</v>
@@ -1594,7 +1586,7 @@
     </row>
     <row r="33" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" s="13">
         <v>2</v>
@@ -1610,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I33" s="13">
         <v>0</v>
@@ -1621,7 +1613,7 @@
     </row>
     <row r="34" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" s="13">
         <v>2</v>
@@ -1637,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>38</v>
@@ -1648,7 +1640,7 @@
     </row>
     <row r="35" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B35" s="13">
         <v>2</v>
@@ -1664,39 +1656,12 @@
         <v>0</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>38</v>
       </c>
       <c r="I35" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="13">
-        <v>118</v>
-      </c>
-      <c r="B36" s="13">
-        <v>2</v>
-      </c>
-      <c r="C36" s="13">
-        <v>2</v>
-      </c>
-      <c r="D36" s="13">
-        <v>1</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13">
-        <v>0</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I36" s="13">
         <v>0</v>
       </c>
     </row>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724EC5E5-9C88-48A1-8C64-FEF2BBE968DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0F0CFB-CC6D-43E3-ACFE-C09B2D36F6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="4215" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20520" yWindow="4140" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -704,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
@@ -887,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
@@ -914,7 +914,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
@@ -941,7 +941,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
@@ -968,7 +968,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
@@ -995,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
@@ -1076,7 +1076,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
@@ -1130,7 +1130,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
@@ -1157,7 +1157,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C17" s="4">
         <v>1</v>
@@ -1346,7 +1346,7 @@
         <v>107</v>
       </c>
       <c r="B24" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="13">
         <v>2</v>
@@ -1663,6 +1663,11 @@
       </c>
       <c r="I35" s="13">
         <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B36" s="13">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0F0CFB-CC6D-43E3-ACFE-C09B2D36F6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8172E3FE-770F-4C82-A391-673BDB00F27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20520" yWindow="4140" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -410,9 +410,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -435,6 +432,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -708,9 +708,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
-    <col min="4" max="5" width="10" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -730,7 +730,7 @@
       <c r="E1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -759,7 +759,7 @@
       <c r="E2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -788,7 +788,7 @@
       <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -811,14 +811,14 @@
       <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -829,30 +829,30 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9">
-        <v>2</v>
-      </c>
-      <c r="F5" s="11">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="A5" s="12">
+        <v>2</v>
+      </c>
+      <c r="B5" s="12">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12">
+        <v>2</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="3">
-        <v>1</v>
+      <c r="I5" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -865,14 +865,14 @@
       <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="D6" s="9">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="11">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -892,14 +892,14 @@
       <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9">
-        <v>1</v>
-      </c>
-      <c r="F7" s="11">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>54</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -910,30 +910,30 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="12">
         <v>5</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="12">
         <v>9</v>
       </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9">
-        <v>2</v>
-      </c>
-      <c r="F8" s="11">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="4">
-        <v>1</v>
+      <c r="I8" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -946,14 +946,14 @@
       <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
         <v>3</v>
       </c>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="10">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>55</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -973,14 +973,14 @@
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
         <v>4</v>
       </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>56</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -1000,14 +1000,14 @@
       <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8">
         <v>4</v>
       </c>
-      <c r="F11" s="11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>58</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -1027,14 +1027,14 @@
       <c r="C12" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
         <v>5</v>
       </c>
-      <c r="F12" s="11">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="F12" s="10">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>57</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -1054,14 +1054,14 @@
       <c r="C13" s="4">
         <v>1</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8">
         <v>6</v>
       </c>
-      <c r="F13" s="11">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -1081,14 +1081,14 @@
       <c r="C14" s="4">
         <v>1</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8">
         <v>7</v>
       </c>
-      <c r="F14" s="11">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="10">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>67</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -1108,14 +1108,14 @@
       <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8">
         <v>7</v>
       </c>
-      <c r="F15" s="11">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -1135,14 +1135,14 @@
       <c r="C16" s="4">
         <v>1</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8">
         <v>7</v>
       </c>
-      <c r="F16" s="11">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -1162,14 +1162,14 @@
       <c r="C17" s="4">
         <v>1</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8">
         <v>7</v>
       </c>
-      <c r="F17" s="11">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="10">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -1180,493 +1180,493 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <v>101</v>
       </c>
-      <c r="B18" s="13">
-        <v>1</v>
-      </c>
-      <c r="C18" s="13">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13">
+      <c r="B18" s="12">
+        <v>1</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12">
         <v>3</v>
       </c>
-      <c r="F18" s="13">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14" t="s">
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <v>102</v>
       </c>
-      <c r="B19" s="13">
-        <v>1</v>
-      </c>
-      <c r="C19" s="13">
-        <v>1</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13">
+      <c r="B19" s="12">
+        <v>1</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12">
         <v>4</v>
       </c>
-      <c r="F19" s="13">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14" t="s">
+      <c r="F19" s="12">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
+      <c r="A20" s="12">
         <v>103</v>
       </c>
-      <c r="B20" s="13">
-        <v>1</v>
-      </c>
-      <c r="C20" s="13">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13">
+      <c r="B20" s="12">
+        <v>1</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12">
         <v>5</v>
       </c>
-      <c r="F20" s="13">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14" t="s">
+      <c r="F20" s="12">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="13">
+      <c r="A21" s="12">
         <v>104</v>
       </c>
-      <c r="B21" s="13">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13">
+      <c r="B21" s="12">
+        <v>1</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12">
         <v>6</v>
       </c>
-      <c r="F21" s="13">
-        <v>0</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="12">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
+      <c r="A22" s="12">
         <v>105</v>
       </c>
-      <c r="B22" s="13">
-        <v>1</v>
-      </c>
-      <c r="C22" s="13">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13">
-        <v>2</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13">
-        <v>0</v>
-      </c>
-      <c r="G22" s="14" t="s">
+      <c r="B22" s="12">
+        <v>1</v>
+      </c>
+      <c r="C22" s="12">
+        <v>2</v>
+      </c>
+      <c r="D22" s="12">
+        <v>2</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="13">
+      <c r="A23" s="12">
         <v>106</v>
       </c>
-      <c r="B23" s="13">
-        <v>1</v>
-      </c>
-      <c r="C23" s="13">
-        <v>2</v>
-      </c>
-      <c r="D23" s="13">
+      <c r="B23" s="12">
+        <v>1</v>
+      </c>
+      <c r="C23" s="12">
+        <v>2</v>
+      </c>
+      <c r="D23" s="12">
         <v>3</v>
       </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-      <c r="G23" s="14" t="s">
+      <c r="E23" s="12"/>
+      <c r="F23" s="12">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="13">
+      <c r="A24" s="12">
         <v>107</v>
       </c>
-      <c r="B24" s="13">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13">
-        <v>2</v>
-      </c>
-      <c r="D24" s="13">
-        <v>1</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14" t="s">
+      <c r="B24" s="12">
+        <v>1</v>
+      </c>
+      <c r="C24" s="12">
+        <v>2</v>
+      </c>
+      <c r="D24" s="12">
+        <v>1</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="13">
+      <c r="A25" s="12">
         <v>108</v>
       </c>
-      <c r="B25" s="13">
-        <v>2</v>
-      </c>
-      <c r="C25" s="13">
-        <v>2</v>
-      </c>
-      <c r="D25" s="13">
-        <v>2</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13">
-        <v>0</v>
-      </c>
-      <c r="G25" s="14" t="s">
+      <c r="B25" s="12">
+        <v>2</v>
+      </c>
+      <c r="C25" s="12">
+        <v>2</v>
+      </c>
+      <c r="D25" s="12">
+        <v>2</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
+      <c r="A26" s="12">
         <v>109</v>
       </c>
-      <c r="B26" s="13">
-        <v>2</v>
-      </c>
-      <c r="C26" s="13">
-        <v>2</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="B26" s="12">
+        <v>2</v>
+      </c>
+      <c r="C26" s="12">
+        <v>2</v>
+      </c>
+      <c r="D26" s="12">
         <v>3</v>
       </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14" t="s">
+      <c r="E26" s="12"/>
+      <c r="F26" s="12">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
+      <c r="A27" s="12">
         <v>110</v>
       </c>
-      <c r="B27" s="13">
-        <v>2</v>
-      </c>
-      <c r="C27" s="13">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13">
+      <c r="B27" s="12">
+        <v>2</v>
+      </c>
+      <c r="C27" s="12">
+        <v>2</v>
+      </c>
+      <c r="D27" s="12">
         <v>3</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14" t="s">
+      <c r="E27" s="12"/>
+      <c r="F27" s="12">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="H27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
+      <c r="A28" s="12">
         <v>111</v>
       </c>
-      <c r="B28" s="13">
-        <v>2</v>
-      </c>
-      <c r="C28" s="13">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="B28" s="12">
+        <v>2</v>
+      </c>
+      <c r="C28" s="12">
+        <v>2</v>
+      </c>
+      <c r="D28" s="12">
         <v>3</v>
       </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13">
-        <v>0</v>
-      </c>
-      <c r="G28" s="14" t="s">
+      <c r="E28" s="12"/>
+      <c r="F28" s="12">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
+      <c r="A29" s="12">
         <v>112</v>
       </c>
-      <c r="B29" s="13">
-        <v>2</v>
-      </c>
-      <c r="C29" s="13">
-        <v>2</v>
-      </c>
-      <c r="D29" s="13">
-        <v>1</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13">
-        <v>0</v>
-      </c>
-      <c r="G29" s="14" t="s">
+      <c r="B29" s="12">
+        <v>2</v>
+      </c>
+      <c r="C29" s="12">
+        <v>2</v>
+      </c>
+      <c r="D29" s="12">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12">
+        <v>0</v>
+      </c>
+      <c r="G29" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
+      <c r="A30" s="12">
         <v>113</v>
       </c>
-      <c r="B30" s="13">
-        <v>2</v>
-      </c>
-      <c r="C30" s="13">
-        <v>2</v>
-      </c>
-      <c r="D30" s="13">
-        <v>1</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13">
-        <v>0</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="B30" s="12">
+        <v>2</v>
+      </c>
+      <c r="C30" s="12">
+        <v>2</v>
+      </c>
+      <c r="D30" s="12">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12">
+        <v>0</v>
+      </c>
+      <c r="G30" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="13">
+      <c r="A31" s="12">
         <v>114</v>
       </c>
-      <c r="B31" s="13">
-        <v>2</v>
-      </c>
-      <c r="C31" s="13">
-        <v>2</v>
-      </c>
-      <c r="D31" s="13">
-        <v>1</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13">
-        <v>0</v>
-      </c>
-      <c r="G31" s="14" t="s">
+      <c r="B31" s="12">
+        <v>2</v>
+      </c>
+      <c r="C31" s="12">
+        <v>2</v>
+      </c>
+      <c r="D31" s="12">
+        <v>1</v>
+      </c>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
+      <c r="A32" s="12">
         <v>115</v>
       </c>
-      <c r="B32" s="13">
-        <v>2</v>
-      </c>
-      <c r="C32" s="13">
-        <v>2</v>
-      </c>
-      <c r="D32" s="13">
-        <v>1</v>
-      </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13">
-        <v>0</v>
-      </c>
-      <c r="G32" s="14" t="s">
+      <c r="B32" s="12">
+        <v>2</v>
+      </c>
+      <c r="C32" s="12">
+        <v>2</v>
+      </c>
+      <c r="D32" s="12">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12">
+        <v>0</v>
+      </c>
+      <c r="G32" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I32" s="13">
+      <c r="I32" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
+      <c r="A33" s="12">
         <v>116</v>
       </c>
-      <c r="B33" s="13">
-        <v>2</v>
-      </c>
-      <c r="C33" s="13">
-        <v>2</v>
-      </c>
-      <c r="D33" s="13">
-        <v>1</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13">
-        <v>0</v>
-      </c>
-      <c r="G33" s="14" t="s">
+      <c r="B33" s="12">
+        <v>2</v>
+      </c>
+      <c r="C33" s="12">
+        <v>2</v>
+      </c>
+      <c r="D33" s="12">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12">
+        <v>0</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H33" s="13" t="s">
+      <c r="H33" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I33" s="13">
+      <c r="I33" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
+      <c r="A34" s="12">
         <v>117</v>
       </c>
-      <c r="B34" s="13">
-        <v>2</v>
-      </c>
-      <c r="C34" s="13">
-        <v>2</v>
-      </c>
-      <c r="D34" s="13">
-        <v>1</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13">
-        <v>0</v>
-      </c>
-      <c r="G34" s="14" t="s">
+      <c r="B34" s="12">
+        <v>2</v>
+      </c>
+      <c r="C34" s="12">
+        <v>2</v>
+      </c>
+      <c r="D34" s="12">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="13">
+      <c r="A35" s="12">
         <v>118</v>
       </c>
-      <c r="B35" s="13">
-        <v>2</v>
-      </c>
-      <c r="C35" s="13">
-        <v>2</v>
-      </c>
-      <c r="D35" s="13">
-        <v>1</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13">
-        <v>0</v>
-      </c>
-      <c r="G35" s="14" t="s">
+      <c r="B35" s="12">
+        <v>2</v>
+      </c>
+      <c r="C35" s="12">
+        <v>2</v>
+      </c>
+      <c r="D35" s="12">
+        <v>1</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12">
+        <v>0</v>
+      </c>
+      <c r="G35" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I35" s="13">
+      <c r="I35" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B36" s="13">
+      <c r="B36" s="12">
         <v>2</v>
       </c>
     </row>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3528F479-E41F-4B5C-9B1C-26A3B737FF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D76C991-786F-4409-825F-B7D24ADB913C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="3315" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="2250" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -175,6 +175,22 @@
   </si>
   <si>
     <t>主基地</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>21,0,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>22,0,20</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
@@ -973,6 +989,84 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D76C991-786F-4409-825F-B7D24ADB913C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A455D08E-07B3-42B0-8FC7-0F78A39DE788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1035" yWindow="2250" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,38 +114,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>15,0,15</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>115,0,115</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>110,0,110</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>120,0,120</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>120,0,110</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>120,0,100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>110,0,120</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,0,120</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>防御塔1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -166,14 +138,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>115,0,105</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>105,0,115</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>主基地</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -182,15 +146,51 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>20,0,20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>21,0,20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>22,0,20</t>
+    <t>25,0,25</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,0,110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,0,90</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>90,0,110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>95,0,95</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,0,95</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>95,0,105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,0,30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>31,0,30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>32,0,30</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>13</v>
@@ -720,10 +720,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4">
         <v>1</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>13</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>14</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>15</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>15</v>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>21</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>16</v>
@@ -902,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H12" s="4">
         <v>1</v>
@@ -928,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H14" s="4">
         <v>0</v>
@@ -980,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H15" s="4">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>41</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H16" s="3">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>42</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H17" s="3">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>43</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H18" s="3">
         <v>0</v>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A455D08E-07B3-42B0-8FC7-0F78A39DE788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E79EFD-8F6F-4841-8F4C-394E783C6B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="2250" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5640" yWindow="2835" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -191,6 +191,14 @@
   </si>
   <si>
     <t>32,0,30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,0,32</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰熊坦克</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -588,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
@@ -1012,7 +1020,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1038,7 +1046,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1064,7 +1072,33 @@
         <v>31</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+      <c r="D19" s="8">
+        <v>3</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E79EFD-8F6F-4841-8F4C-394E783C6B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24650E1A-88B1-40BB-9A27-69E5273D7D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5640" yWindow="2835" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1020,7 +1020,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1046,7 +1046,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1072,7 +1072,7 @@
         <v>31</v>
       </c>
       <c r="H18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24650E1A-88B1-40BB-9A27-69E5273D7D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90360893-958D-4008-A2E4-22C684A4B21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="2835" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20670" yWindow="2850" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
         <v>45</v>
       </c>
       <c r="H19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90360893-958D-4008-A2E4-22C684A4B21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD565389-F0B3-41FF-9D75-E25413F3FABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20670" yWindow="2850" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="4635" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -864,7 +864,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1098,7 +1098,7 @@
         <v>45</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD565389-F0B3-41FF-9D75-E25413F3FABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED5FCA4-31B7-43A1-AB32-7232D8EC57CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4635" yWindow="4635" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
@@ -1020,7 +1020,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1028,7 +1028,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -1046,7 +1046,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1054,7 +1054,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
@@ -1072,7 +1072,7 @@
         <v>31</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1086,7 +1086,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="10">
         <v>0</v>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED5FCA4-31B7-43A1-AB32-7232D8EC57CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7CB543-60A7-453E-BC8D-B4CABDE692F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="4635" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -1020,7 +1020,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1046,7 +1046,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1072,7 +1072,7 @@
         <v>31</v>
       </c>
       <c r="H18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1098,7 +1098,7 @@
         <v>45</v>
       </c>
       <c r="H19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7CB543-60A7-453E-BC8D-B4CABDE692F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7563BC-616C-4950-8508-F30F34597B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1305" yWindow="1920" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -194,11 +194,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>30,0,32</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>灰熊坦克</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,32</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1020,7 +1020,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1046,7 +1046,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1072,7 +1072,7 @@
         <v>31</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1092,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7563BC-616C-4950-8508-F30F34597B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D74E9-BB4F-44EB-8002-51DC7E80F0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1305" yWindow="1920" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1020,7 +1020,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1046,7 +1046,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1072,7 +1072,7 @@
         <v>31</v>
       </c>
       <c r="H18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1098,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="H19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D74E9-BB4F-44EB-8002-51DC7E80F0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DFAC9F-33B6-4A06-BB38-8957C8B90653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="1920" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17430" yWindow="3675" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfInitUnits" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -74,18 +74,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>主基地</t>
-  </si>
-  <si>
-    <t>采矿场</t>
-  </si>
-  <si>
-    <t>电厂</t>
-  </si>
-  <si>
-    <t>坦克工厂</t>
-  </si>
-  <si>
     <t>ConfID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -102,10 +90,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>兵营</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Enabled</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -122,30 +106,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>防御塔2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御塔3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御塔4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>105,0,105</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>主基地</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>士兵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>25,0,25</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -174,14 +134,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>105,0,95</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>95,0,105</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>30,0,30</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -194,11 +146,38 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>灰熊坦克</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>20,0,32</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前线指挥枢纽</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>反重装步兵</t>
+  </si>
+  <si>
+    <t>反重装步兵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重装坦克</t>
+  </si>
+  <si>
+    <t>资源回收站</t>
+  </si>
+  <si>
+    <t>模块化动力阵列</t>
+  </si>
+  <si>
+    <t>整备营区</t>
+  </si>
+  <si>
+    <t>重型装甲装配厂</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻型载具工场</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -596,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="10.75" customWidth="1"/>
@@ -618,7 +597,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>3</v>
@@ -630,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -644,7 +623,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>7</v>
@@ -656,7 +635,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -670,10 +649,10 @@
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>11</v>
@@ -682,7 +661,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -702,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
@@ -728,10 +707,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" s="4">
         <v>1</v>
@@ -754,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
@@ -780,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H7" s="4">
         <v>1</v>
@@ -806,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H8" s="4">
         <v>1</v>
@@ -826,16 +805,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" s="10">
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H9" s="4">
         <v>1</v>
@@ -858,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
@@ -878,16 +857,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
@@ -904,16 +883,16 @@
         <v>1</v>
       </c>
       <c r="D12" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H12" s="4">
         <v>1</v>
@@ -921,184 +900,106 @@
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4">
-        <v>9</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
       </c>
       <c r="D13" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E13" s="10">
         <v>0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="4">
+        <v>28</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4">
-        <v>9</v>
-      </c>
-      <c r="C14" s="4">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2</v>
       </c>
       <c r="D14" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E14" s="10">
         <v>0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="4">
+        <v>29</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
       </c>
       <c r="D15" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E15" s="10">
         <v>0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="4">
+        <v>30</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
       </c>
       <c r="D16" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="10">
         <v>0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3">
-        <v>9</v>
-      </c>
-      <c r="C17" s="3">
-        <v>2</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3">
-        <v>9</v>
-      </c>
-      <c r="C18" s="3">
-        <v>2</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3">
-        <v>2</v>
-      </c>
-      <c r="D19" s="8">
-        <v>2</v>
-      </c>
-      <c r="E19" s="10">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DFAC9F-33B6-4A06-BB38-8957C8B90653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5D7B9F-7DAC-4983-B1BB-8C44DBE46C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17430" yWindow="3675" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -903,7 +903,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13" s="3">
         <v>2</v>
@@ -921,7 +921,7 @@
         <v>34</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -929,13 +929,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
       </c>
       <c r="D14" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="10">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>33</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -955,13 +955,13 @@
         <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C15" s="3">
         <v>2</v>
       </c>
       <c r="D15" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="10">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>33</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -999,7 +999,7 @@
         <v>35</v>
       </c>
       <c r="H16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/InitUnits.xlsx
+++ b/config/excel/InitUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5D7B9F-7DAC-4983-B1BB-8C44DBE46C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25076CCE-5A89-466E-B895-3A874BFA413F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17430" yWindow="3675" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -921,7 +921,7 @@
         <v>34</v>
       </c>
       <c r="H13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -947,7 +947,7 @@
         <v>33</v>
       </c>
       <c r="H14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -973,7 +973,7 @@
         <v>33</v>
       </c>
       <c r="H15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -981,7 +981,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
